--- a/Final Results/Statistical_Comparison.xlsx
+++ b/Final Results/Statistical_Comparison.xlsx
@@ -1,43 +1,117 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deepanshu Postdoc MSU\Research\GECCO 2025\2. Bench-iMCDM\Source Code\Bench-iMCDM_GECCO26\Final Results\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9A176D-1F80-4002-9099-3A87EBAC0EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+  <si>
+    <t>$h_E$</t>
+  </si>
+  <si>
+    <t>$\eta_E$</t>
+  </si>
+  <si>
+    <t>$\Phi_E$</t>
+  </si>
+  <si>
+    <t>$N_{evl}</t>
+  </si>
+  <si>
+    <t>MachDM-STEM</t>
+  </si>
+  <si>
+    <t>MachDM-STOM</t>
+  </si>
+  <si>
+    <t>MachDM-GUESS</t>
+  </si>
+  <si>
+    <t>MachDM-NIMBUS</t>
+  </si>
+  <si>
+    <t>Examples</t>
+  </si>
+  <si>
+    <t>WATER</t>
+  </si>
+  <si>
+    <t>Knee 2-obj.</t>
+  </si>
+  <si>
+    <t>Knee 3-obj.</t>
+  </si>
+  <si>
+    <t>Crash.</t>
+  </si>
+  <si>
+    <t>Car Side</t>
+  </si>
+  <si>
+    <t xml:space="preserve">River </t>
+  </si>
+  <si>
+    <t>DTLZ2 8-obj.</t>
+  </si>
+  <si>
+    <t>NIMBUS Bench.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -46,93 +120,87 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,497 +488,541 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:P9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:R11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>STEM_Iter</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>STEM_Success</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>STEM_Violation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>STEM_Eval</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>STOM_Iter</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>STOM_Success</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>STOM_Violation</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>STOM_Eval</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>GUESS_Iter</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>GUESS_Success</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>GUESS_Violation</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>GUESS_Eval</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>NIMBUS_Iter</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>NIMBUS_Success</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>NIMBUS_Violation</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>NIMBUS_Eval</t>
-        </is>
-      </c>
+    <row r="2" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="3" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B3" s="6"/>
+      <c r="C3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4">
         <v>6</v>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
         <v>0.125</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F4" s="2">
         <v>140000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G4" s="4">
         <v>7</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
         <v>0.25</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J4" s="2">
         <v>160000</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K4" s="4">
         <v>3.5</v>
       </c>
-      <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L4" s="4">
+        <v>1</v>
+      </c>
+      <c r="M4" s="4">
         <v>0.25</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N4" s="2">
         <v>90000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O4" s="4">
         <v>6.5</v>
       </c>
-      <c r="N2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" t="n">
+      <c r="P4" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="4">
         <v>0.125</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R4" s="2">
         <v>150000</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
+      <c r="D5" s="4">
         <v>0.5</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E5" s="4">
         <v>0.25</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F5" s="2">
         <v>140000</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G5" s="4">
         <v>5.5</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J5" s="2">
         <v>130000</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K5" s="4">
         <v>5</v>
       </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="L5" s="4">
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="N5" s="2">
         <v>120000</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O5" s="4">
         <v>6</v>
       </c>
-      <c r="N3" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="P5" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="R5" s="2">
         <v>140000</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4">
         <v>5</v>
       </c>
-      <c r="B4" t="n">
+      <c r="D6" s="4">
         <v>0.5</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="E6" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F6" s="2">
         <v>120000</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G6" s="4">
         <v>4</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
         <v>100000</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K6" s="4">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="L6" s="4">
+        <v>1</v>
+      </c>
+      <c r="M6" s="4">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2">
         <v>60000</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O6" s="4">
         <v>6</v>
       </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="P6" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="4">
+        <v>0.16666666666666671</v>
+      </c>
+      <c r="R6" s="2">
         <v>140000</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
+      <c r="D7" s="4">
         <v>0.5</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="E7" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F7" s="2">
         <v>180000</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G7" s="4">
         <v>9</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7" s="4">
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="J7" s="2">
         <v>200000</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K7" s="4">
         <v>3.5</v>
       </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="L7" s="4">
+        <v>1</v>
+      </c>
+      <c r="M7" s="4">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2">
         <v>90000</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O7" s="4">
         <v>7.5</v>
       </c>
-      <c r="N5" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="P7" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>0</v>
+      </c>
+      <c r="R7" s="2">
         <v>170000</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="8" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4">
         <v>6</v>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" t="n">
+      <c r="D8" s="4">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
         <v>0.25</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F8" s="2">
         <v>140000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G8" s="4">
         <v>11</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H8" s="4">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4">
         <v>0.5</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J8" s="2">
         <v>240000</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K8" s="4">
         <v>6</v>
       </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="L8" s="4">
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2">
         <v>140000</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O8" s="4">
         <v>6.5</v>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="P8" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="4">
         <v>0.25</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R8" s="2">
         <v>150000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="9" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B9" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="4">
         <v>4</v>
       </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="D9" s="4">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
         <v>0.3</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F9" s="2">
         <v>100000</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G9" s="4">
         <v>11</v>
       </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H9" s="4">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4">
         <v>0.2</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J9" s="2">
         <v>240000</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K9" s="4">
         <v>4.5</v>
       </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="L9" s="4">
+        <v>1</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
         <v>110000</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O9" s="4">
         <v>4</v>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
+      <c r="P9" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="4">
         <v>0.2</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R9" s="2">
         <v>100000</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="10" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="4">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="D10" s="4">
+        <v>0</v>
+      </c>
+      <c r="E10" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="F10" s="2">
         <v>160000</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G10" s="4">
         <v>11</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H10" s="4">
+        <v>0</v>
+      </c>
+      <c r="I10" s="4">
         <v>0.25</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J10" s="2">
         <v>240000</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K10" s="4">
         <v>11</v>
       </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="L10" s="4">
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="N10" s="2">
         <v>240000</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O10" s="4">
         <v>8.5</v>
       </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
+      <c r="P10" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="4">
         <v>0.375</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R10" s="2">
         <v>190000</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="11" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="4">
         <v>11</v>
       </c>
-      <c r="B9" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="D11" s="4">
+        <v>0</v>
+      </c>
+      <c r="E11" s="4">
         <v>0.34375</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F11" s="2">
         <v>240000</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G11" s="4">
         <v>11</v>
       </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="H11" s="4">
+        <v>0</v>
+      </c>
+      <c r="I11" s="4">
         <v>0.53125</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J11" s="2">
         <v>240000</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K11" s="4">
         <v>10.5</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L11" s="4">
         <v>0.5</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M11" s="4">
         <v>0.3125</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N11" s="2">
         <v>230000</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O11" s="4">
         <v>11</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P11" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="4">
         <v>0.5625</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R11" s="2">
         <v>240000</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:R2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>